--- a/artfynd/A 48352-2022 artfynd.xlsx
+++ b/artfynd/A 48352-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48352-2022 artfynd.xlsx
+++ b/artfynd/A 48352-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>69507145</v>
       </c>
       <c r="B2" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685099.4138292701</v>
+        <v>685099</v>
       </c>
       <c r="R2" t="n">
-        <v>6687390.876122851</v>
+        <v>6687391</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2003-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69551075</v>
+        <v>69529594</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685129.5236428662</v>
+        <v>685076</v>
       </c>
       <c r="R3" t="n">
-        <v>6687385.947111289</v>
+        <v>6687323</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,24 +868,14 @@
           <t>2003-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2003-10-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca. 10 ex. i mossvegetation under äldre gran.</t>
+          <t>7 ex. under gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,42 +907,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69563217</v>
+        <v>75891282</v>
       </c>
       <c r="B4" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>4405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -986,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685040.0347744998</v>
+        <v>685115</v>
       </c>
       <c r="R4" t="n">
-        <v>6687335.195314368</v>
+        <v>6687378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,27 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-10-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-10-10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca. 10 ex.</t>
+          <t>3 ex. i mossvegetation under gran och hassel.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1005,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre, örtrik barrskog.</t>
+          <t>Äldre, örtrik barrskog med inslag av hassel.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,42 +1023,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75891282</v>
+        <v>69563217</v>
       </c>
       <c r="B5" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4405</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685114.5136786308</v>
+        <v>685040</v>
       </c>
       <c r="R5" t="n">
-        <v>6687377.731937977</v>
+        <v>6687335</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,27 +1097,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2003-10-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3 ex. i mossvegetation under gran och hassel.</t>
+          <t>Ca. 10 ex.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre, örtrik barrskog med inslag av hassel.</t>
+          <t>Äldre, örtrik barrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 48352-2022 artfynd.xlsx
+++ b/artfynd/A 48352-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69507145</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69529594</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75891282</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,8 +1156,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69563217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>